--- a/artfynd/A 63229-2020 artfynd.xlsx
+++ b/artfynd/A 63229-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63229-2020 artfynd.xlsx
+++ b/artfynd/A 63229-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY148"/>
+  <dimension ref="A1:AY111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9440,10 +9440,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112606268</v>
+        <v>112610313</v>
       </c>
       <c r="B77" t="n">
-        <v>91032</v>
+        <v>55842</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9456,34 +9456,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>760235</v>
+        <v>760225</v>
       </c>
       <c r="R77" t="n">
-        <v>7135369</v>
+        <v>7135392</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9510,12 +9510,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -9547,7 +9547,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112606271</v>
+        <v>112610340</v>
       </c>
       <c r="B78" t="n">
         <v>77856</v>
@@ -9583,14 +9583,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>760209</v>
+        <v>760248</v>
       </c>
       <c r="R78" t="n">
-        <v>7135313</v>
+        <v>7135251</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9617,12 +9617,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -9654,10 +9654,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>112610264</v>
+        <v>112610472</v>
       </c>
       <c r="B79" t="n">
-        <v>88855</v>
+        <v>91076</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9670,21 +9670,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>760107</v>
+        <v>760245</v>
       </c>
       <c r="R79" t="n">
-        <v>7135388</v>
+        <v>7135157</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9724,12 +9724,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9761,10 +9761,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112610313</v>
+        <v>112610311</v>
       </c>
       <c r="B80" t="n">
-        <v>55842</v>
+        <v>91044</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9777,21 +9777,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9804,7 +9804,7 @@
         <v>760225</v>
       </c>
       <c r="R80" t="n">
-        <v>7135392</v>
+        <v>7135378</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9868,10 +9868,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112610340</v>
+        <v>112610357</v>
       </c>
       <c r="B81" t="n">
-        <v>77856</v>
+        <v>77891</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9884,21 +9884,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>760248</v>
+        <v>760201</v>
       </c>
       <c r="R81" t="n">
-        <v>7135251</v>
+        <v>7135137</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9938,12 +9938,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9975,7 +9975,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112606292</v>
+        <v>112610331</v>
       </c>
       <c r="B82" t="n">
         <v>77891</v>
@@ -10011,14 +10011,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>760213</v>
+        <v>760277</v>
       </c>
       <c r="R82" t="n">
-        <v>7135141</v>
+        <v>7135266</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10045,12 +10045,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112610472</v>
+        <v>112610267</v>
       </c>
       <c r="B83" t="n">
-        <v>91076</v>
+        <v>91036</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10094,25 +10094,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>760245</v>
+        <v>760193</v>
       </c>
       <c r="R83" t="n">
-        <v>7135157</v>
+        <v>7135195</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -10189,10 +10189,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112610311</v>
+        <v>112610457</v>
       </c>
       <c r="B84" t="n">
-        <v>91044</v>
+        <v>91076</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10201,25 +10201,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10229,10 +10229,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>760225</v>
+        <v>760202</v>
       </c>
       <c r="R84" t="n">
-        <v>7135378</v>
+        <v>7135145</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -10296,10 +10296,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112606283</v>
+        <v>112610343</v>
       </c>
       <c r="B85" t="n">
-        <v>91032</v>
+        <v>91076</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10308,38 +10308,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>760238</v>
+        <v>760179</v>
       </c>
       <c r="R85" t="n">
-        <v>7135196</v>
+        <v>7135140</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10366,12 +10366,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -10403,10 +10403,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112610357</v>
+        <v>112610462</v>
       </c>
       <c r="B86" t="n">
-        <v>77891</v>
+        <v>91024</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10419,21 +10419,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>185</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10443,10 +10443,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>760201</v>
+        <v>760041</v>
       </c>
       <c r="R86" t="n">
-        <v>7135137</v>
+        <v>7135319</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10473,12 +10473,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -10510,10 +10510,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112610331</v>
+        <v>112610319</v>
       </c>
       <c r="B87" t="n">
-        <v>77891</v>
+        <v>56623</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10526,21 +10526,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10550,10 +10550,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>760277</v>
+        <v>760339</v>
       </c>
       <c r="R87" t="n">
-        <v>7135266</v>
+        <v>7135370</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10617,10 +10617,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112610267</v>
+        <v>112610330</v>
       </c>
       <c r="B88" t="n">
-        <v>91036</v>
+        <v>56623</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10629,25 +10629,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10657,10 +10657,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>760193</v>
+        <v>760282</v>
       </c>
       <c r="R88" t="n">
-        <v>7135195</v>
+        <v>7135261</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10687,12 +10687,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10724,7 +10724,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112610327</v>
+        <v>112610337</v>
       </c>
       <c r="B89" t="n">
         <v>91055</v>
@@ -10764,10 +10764,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>760303</v>
+        <v>760300</v>
       </c>
       <c r="R89" t="n">
-        <v>7135247</v>
+        <v>7135241</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10831,10 +10831,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112610324</v>
+        <v>112610326</v>
       </c>
       <c r="B90" t="n">
-        <v>77856</v>
+        <v>91055</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10847,21 +10847,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>760320</v>
+        <v>760310</v>
       </c>
       <c r="R90" t="n">
-        <v>7135331</v>
+        <v>7135304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112606278</v>
+        <v>112610335</v>
       </c>
       <c r="B91" t="n">
-        <v>91055</v>
+        <v>91024</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10954,34 +10954,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>760070</v>
+        <v>760265</v>
       </c>
       <c r="R91" t="n">
-        <v>7135305</v>
+        <v>7135222</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11008,12 +11008,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -11045,10 +11045,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112610457</v>
+        <v>112610329</v>
       </c>
       <c r="B92" t="n">
-        <v>91076</v>
+        <v>91044</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11057,25 +11057,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11085,10 +11085,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>760202</v>
+        <v>760256</v>
       </c>
       <c r="R92" t="n">
-        <v>7135145</v>
+        <v>7135230</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11115,12 +11115,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -11152,10 +11152,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112610356</v>
+        <v>112610268</v>
       </c>
       <c r="B93" t="n">
-        <v>91220</v>
+        <v>88855</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11168,21 +11168,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>760208</v>
+        <v>760192</v>
       </c>
       <c r="R93" t="n">
-        <v>7135121</v>
+        <v>7135201</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11222,12 +11222,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -11259,7 +11259,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112606281</v>
+        <v>112610341</v>
       </c>
       <c r="B94" t="n">
         <v>91032</v>
@@ -11295,14 +11295,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>760182</v>
+        <v>760174</v>
       </c>
       <c r="R94" t="n">
-        <v>7135252</v>
+        <v>7135195</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11329,12 +11329,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -11366,10 +11366,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112610343</v>
+        <v>112610338</v>
       </c>
       <c r="B95" t="n">
-        <v>91076</v>
+        <v>77891</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11382,21 +11382,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5449</v>
+        <v>185</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11406,10 +11406,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>760179</v>
+        <v>760274</v>
       </c>
       <c r="R95" t="n">
-        <v>7135140</v>
+        <v>7135265</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11473,10 +11473,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112606273</v>
+        <v>112610308</v>
       </c>
       <c r="B96" t="n">
-        <v>90168</v>
+        <v>77856</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11485,38 +11485,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5420</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>760098</v>
+        <v>760205</v>
       </c>
       <c r="R96" t="n">
-        <v>7135383</v>
+        <v>7135306</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -11580,10 +11580,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112606280</v>
+        <v>112610334</v>
       </c>
       <c r="B97" t="n">
-        <v>89924</v>
+        <v>77856</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11592,38 +11592,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>760113</v>
+        <v>760277</v>
       </c>
       <c r="R97" t="n">
-        <v>7135204</v>
+        <v>7135267</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -11687,7 +11687,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112606279</v>
+        <v>112610463</v>
       </c>
       <c r="B98" t="n">
         <v>91032</v>
@@ -11723,14 +11723,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>760069</v>
+        <v>760028</v>
       </c>
       <c r="R98" t="n">
-        <v>7135268</v>
+        <v>7135372</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11757,12 +11757,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -11794,10 +11794,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>112610460</v>
+        <v>112610323</v>
       </c>
       <c r="B99" t="n">
-        <v>91032</v>
+        <v>77856</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11806,25 +11806,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11834,10 +11834,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>760079</v>
+        <v>760318</v>
       </c>
       <c r="R99" t="n">
-        <v>7135269</v>
+        <v>7135346</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11864,12 +11864,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -11901,10 +11901,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>112610462</v>
+        <v>112610320</v>
       </c>
       <c r="B100" t="n">
-        <v>91024</v>
+        <v>91032</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11913,25 +11913,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11941,10 +11941,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>760041</v>
+        <v>760335</v>
       </c>
       <c r="R100" t="n">
-        <v>7135319</v>
+        <v>7135401</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11971,12 +11971,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -12008,10 +12008,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>112606267</v>
+        <v>112610456</v>
       </c>
       <c r="B101" t="n">
-        <v>91055</v>
+        <v>91032</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12020,38 +12020,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>760305</v>
+        <v>760231</v>
       </c>
       <c r="R101" t="n">
-        <v>7135245</v>
+        <v>7135122</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12078,12 +12078,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -12115,10 +12115,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>112610319</v>
+        <v>112610314</v>
       </c>
       <c r="B102" t="n">
-        <v>56623</v>
+        <v>91032</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12127,25 +12127,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12155,10 +12155,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>760339</v>
+        <v>760263</v>
       </c>
       <c r="R102" t="n">
-        <v>7135370</v>
+        <v>7135399</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12222,7 +12222,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>112610330</v>
+        <v>112610316</v>
       </c>
       <c r="B103" t="n">
         <v>56623</v>
@@ -12262,10 +12262,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>760282</v>
+        <v>760323</v>
       </c>
       <c r="R103" t="n">
-        <v>7135261</v>
+        <v>7135375</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12329,10 +12329,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>112610337</v>
+        <v>112610317</v>
       </c>
       <c r="B104" t="n">
-        <v>91055</v>
+        <v>89735</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12341,25 +12341,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12369,10 +12369,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>760300</v>
+        <v>760321</v>
       </c>
       <c r="R104" t="n">
-        <v>7135241</v>
+        <v>7135387</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12436,10 +12436,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>112610326</v>
+        <v>112610469</v>
       </c>
       <c r="B105" t="n">
-        <v>91055</v>
+        <v>77856</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12452,21 +12452,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12476,10 +12476,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>760310</v>
+        <v>760205</v>
       </c>
       <c r="R105" t="n">
-        <v>7135304</v>
+        <v>7135302</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12506,12 +12506,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -12543,10 +12543,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>112610335</v>
+        <v>112610458</v>
       </c>
       <c r="B106" t="n">
-        <v>91024</v>
+        <v>91032</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12555,25 +12555,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12583,10 +12583,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>760265</v>
+        <v>760176</v>
       </c>
       <c r="R106" t="n">
-        <v>7135222</v>
+        <v>7135166</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12613,12 +12613,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -12650,10 +12650,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>112610329</v>
+        <v>112610262</v>
       </c>
       <c r="B107" t="n">
-        <v>91044</v>
+        <v>90168</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12666,21 +12666,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4366</v>
+        <v>5420</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12690,10 +12690,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>760256</v>
+        <v>760099</v>
       </c>
       <c r="R107" t="n">
-        <v>7135230</v>
+        <v>7135384</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12720,12 +12720,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2022-09-30</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -12757,10 +12757,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>112606285</v>
+        <v>112610310</v>
       </c>
       <c r="B108" t="n">
-        <v>91036</v>
+        <v>56768</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12769,38 +12769,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>760189</v>
+        <v>760210</v>
       </c>
       <c r="R108" t="n">
-        <v>7135198</v>
+        <v>7135372</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12827,12 +12827,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -12864,10 +12864,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>112606272</v>
+        <v>112610354</v>
       </c>
       <c r="B109" t="n">
-        <v>91032</v>
+        <v>77891</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12876,38 +12876,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>760049</v>
+        <v>760211</v>
       </c>
       <c r="R109" t="n">
-        <v>7135410</v>
+        <v>7135137</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12934,12 +12934,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -12971,10 +12971,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>112610268</v>
+        <v>112610346</v>
       </c>
       <c r="B110" t="n">
-        <v>88855</v>
+        <v>56768</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12987,21 +12987,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13011,10 +13011,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>760192</v>
+        <v>760200</v>
       </c>
       <c r="R110" t="n">
-        <v>7135201</v>
+        <v>7135128</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13041,12 +13041,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -13078,10 +13078,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>112606291</v>
+        <v>112610471</v>
       </c>
       <c r="B111" t="n">
-        <v>91220</v>
+        <v>91032</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13090,38 +13090,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Botsmark, Vb</t>
+          <t>Gravfors, Vb</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>760206</v>
+        <v>760240</v>
       </c>
       <c r="R111" t="n">
-        <v>7135116</v>
+        <v>7135158</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13148,12 +13148,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -13182,3965 +13182,6 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>112606284</v>
-      </c>
-      <c r="B112" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q112" t="n">
-        <v>760204</v>
-      </c>
-      <c r="R112" t="n">
-        <v>7135219</v>
-      </c>
-      <c r="S112" t="n">
-        <v>10</v>
-      </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT112" t="inlineStr"/>
-      <c r="AW112" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>112606269</v>
-      </c>
-      <c r="B113" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q113" t="n">
-        <v>760351</v>
-      </c>
-      <c r="R113" t="n">
-        <v>7135387</v>
-      </c>
-      <c r="S113" t="n">
-        <v>10</v>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT113" t="inlineStr"/>
-      <c r="AW113" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>112610341</v>
-      </c>
-      <c r="B114" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q114" t="n">
-        <v>760174</v>
-      </c>
-      <c r="R114" t="n">
-        <v>7135195</v>
-      </c>
-      <c r="S114" t="n">
-        <v>10</v>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT114" t="inlineStr"/>
-      <c r="AW114" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>112606288</v>
-      </c>
-      <c r="B115" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q115" t="n">
-        <v>760192</v>
-      </c>
-      <c r="R115" t="n">
-        <v>7135199</v>
-      </c>
-      <c r="S115" t="n">
-        <v>10</v>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT115" t="inlineStr"/>
-      <c r="AW115" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>112606277</v>
-      </c>
-      <c r="B116" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q116" t="n">
-        <v>760096</v>
-      </c>
-      <c r="R116" t="n">
-        <v>7135300</v>
-      </c>
-      <c r="S116" t="n">
-        <v>10</v>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT116" t="inlineStr"/>
-      <c r="AW116" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>112610338</v>
-      </c>
-      <c r="B117" t="n">
-        <v>77891</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>185</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q117" t="n">
-        <v>760274</v>
-      </c>
-      <c r="R117" t="n">
-        <v>7135265</v>
-      </c>
-      <c r="S117" t="n">
-        <v>10</v>
-      </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD117" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE117" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG117" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT117" t="inlineStr"/>
-      <c r="AW117" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>112606282</v>
-      </c>
-      <c r="B118" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q118" t="n">
-        <v>760214</v>
-      </c>
-      <c r="R118" t="n">
-        <v>7135253</v>
-      </c>
-      <c r="S118" t="n">
-        <v>10</v>
-      </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT118" t="inlineStr"/>
-      <c r="AW118" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>112610308</v>
-      </c>
-      <c r="B119" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q119" t="n">
-        <v>760205</v>
-      </c>
-      <c r="R119" t="n">
-        <v>7135306</v>
-      </c>
-      <c r="S119" t="n">
-        <v>10</v>
-      </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT119" t="inlineStr"/>
-      <c r="AW119" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>112610334</v>
-      </c>
-      <c r="B120" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q120" t="n">
-        <v>760277</v>
-      </c>
-      <c r="R120" t="n">
-        <v>7135267</v>
-      </c>
-      <c r="S120" t="n">
-        <v>10</v>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT120" t="inlineStr"/>
-      <c r="AW120" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>112606266</v>
-      </c>
-      <c r="B121" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q121" t="n">
-        <v>760365</v>
-      </c>
-      <c r="R121" t="n">
-        <v>7135292</v>
-      </c>
-      <c r="S121" t="n">
-        <v>10</v>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT121" t="inlineStr"/>
-      <c r="AW121" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>112610463</v>
-      </c>
-      <c r="B122" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q122" t="n">
-        <v>760028</v>
-      </c>
-      <c r="R122" t="n">
-        <v>7135372</v>
-      </c>
-      <c r="S122" t="n">
-        <v>10</v>
-      </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD122" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE122" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG122" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT122" t="inlineStr"/>
-      <c r="AW122" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>112606274</v>
-      </c>
-      <c r="B123" t="n">
-        <v>88855</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Vaddporing</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Anomoporia kamtschatica</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q123" t="n">
-        <v>760106</v>
-      </c>
-      <c r="R123" t="n">
-        <v>7135387</v>
-      </c>
-      <c r="S123" t="n">
-        <v>10</v>
-      </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD123" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG123" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT123" t="inlineStr"/>
-      <c r="AW123" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>112606286</v>
-      </c>
-      <c r="B124" t="n">
-        <v>88855</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Vaddporing</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Anomoporia kamtschatica</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q124" t="n">
-        <v>760195</v>
-      </c>
-      <c r="R124" t="n">
-        <v>7135197</v>
-      </c>
-      <c r="S124" t="n">
-        <v>10</v>
-      </c>
-      <c r="T124" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT124" t="inlineStr"/>
-      <c r="AW124" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>112610323</v>
-      </c>
-      <c r="B125" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q125" t="n">
-        <v>760318</v>
-      </c>
-      <c r="R125" t="n">
-        <v>7135346</v>
-      </c>
-      <c r="S125" t="n">
-        <v>10</v>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT125" t="inlineStr"/>
-      <c r="AW125" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>112606275</v>
-      </c>
-      <c r="B126" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q126" t="n">
-        <v>760097</v>
-      </c>
-      <c r="R126" t="n">
-        <v>7135378</v>
-      </c>
-      <c r="S126" t="n">
-        <v>10</v>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT126" t="inlineStr"/>
-      <c r="AW126" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>112606270</v>
-      </c>
-      <c r="B127" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q127" t="n">
-        <v>760309</v>
-      </c>
-      <c r="R127" t="n">
-        <v>7135342</v>
-      </c>
-      <c r="S127" t="n">
-        <v>10</v>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT127" t="inlineStr"/>
-      <c r="AW127" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>112610320</v>
-      </c>
-      <c r="B128" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q128" t="n">
-        <v>760335</v>
-      </c>
-      <c r="R128" t="n">
-        <v>7135401</v>
-      </c>
-      <c r="S128" t="n">
-        <v>10</v>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT128" t="inlineStr"/>
-      <c r="AW128" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>112610456</v>
-      </c>
-      <c r="B129" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q129" t="n">
-        <v>760231</v>
-      </c>
-      <c r="R129" t="n">
-        <v>7135122</v>
-      </c>
-      <c r="S129" t="n">
-        <v>10</v>
-      </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT129" t="inlineStr"/>
-      <c r="AW129" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>112610314</v>
-      </c>
-      <c r="B130" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q130" t="n">
-        <v>760263</v>
-      </c>
-      <c r="R130" t="n">
-        <v>7135399</v>
-      </c>
-      <c r="S130" t="n">
-        <v>10</v>
-      </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT130" t="inlineStr"/>
-      <c r="AW130" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>112610316</v>
-      </c>
-      <c r="B131" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q131" t="n">
-        <v>760323</v>
-      </c>
-      <c r="R131" t="n">
-        <v>7135375</v>
-      </c>
-      <c r="S131" t="n">
-        <v>10</v>
-      </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT131" t="inlineStr"/>
-      <c r="AW131" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>112610317</v>
-      </c>
-      <c r="B132" t="n">
-        <v>89735</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q132" t="n">
-        <v>760321</v>
-      </c>
-      <c r="R132" t="n">
-        <v>7135387</v>
-      </c>
-      <c r="S132" t="n">
-        <v>10</v>
-      </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT132" t="inlineStr"/>
-      <c r="AW132" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>112610469</v>
-      </c>
-      <c r="B133" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q133" t="n">
-        <v>760205</v>
-      </c>
-      <c r="R133" t="n">
-        <v>7135302</v>
-      </c>
-      <c r="S133" t="n">
-        <v>10</v>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT133" t="inlineStr"/>
-      <c r="AW133" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>112606290</v>
-      </c>
-      <c r="B134" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q134" t="n">
-        <v>760174</v>
-      </c>
-      <c r="R134" t="n">
-        <v>7135092</v>
-      </c>
-      <c r="S134" t="n">
-        <v>10</v>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT134" t="inlineStr"/>
-      <c r="AW134" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>112610355</v>
-      </c>
-      <c r="B135" t="n">
-        <v>77891</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
-        <v>185</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q135" t="n">
-        <v>760207</v>
-      </c>
-      <c r="R135" t="n">
-        <v>7135138</v>
-      </c>
-      <c r="S135" t="n">
-        <v>10</v>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD135" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG135" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT135" t="inlineStr"/>
-      <c r="AW135" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX135" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>112610470</v>
-      </c>
-      <c r="B136" t="n">
-        <v>89924</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
-        <v>1503</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Gräddporing</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Sidera lenis</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q136" t="n">
-        <v>760118</v>
-      </c>
-      <c r="R136" t="n">
-        <v>7135192</v>
-      </c>
-      <c r="S136" t="n">
-        <v>10</v>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT136" t="inlineStr"/>
-      <c r="AW136" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX136" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>112610459</v>
-      </c>
-      <c r="B137" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q137" t="n">
-        <v>760118</v>
-      </c>
-      <c r="R137" t="n">
-        <v>7135211</v>
-      </c>
-      <c r="S137" t="n">
-        <v>10</v>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD137" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE137" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG137" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT137" t="inlineStr"/>
-      <c r="AW137" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX137" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>112606289</v>
-      </c>
-      <c r="B138" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q138" t="n">
-        <v>760180</v>
-      </c>
-      <c r="R138" t="n">
-        <v>7135169</v>
-      </c>
-      <c r="S138" t="n">
-        <v>10</v>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT138" t="inlineStr"/>
-      <c r="AW138" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX138" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>112610458</v>
-      </c>
-      <c r="B139" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q139" t="n">
-        <v>760176</v>
-      </c>
-      <c r="R139" t="n">
-        <v>7135166</v>
-      </c>
-      <c r="S139" t="n">
-        <v>10</v>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD139" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG139" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT139" t="inlineStr"/>
-      <c r="AW139" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX139" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>112606265</v>
-      </c>
-      <c r="B140" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q140" t="n">
-        <v>760386</v>
-      </c>
-      <c r="R140" t="n">
-        <v>7135321</v>
-      </c>
-      <c r="S140" t="n">
-        <v>10</v>
-      </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT140" t="inlineStr"/>
-      <c r="AW140" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX140" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>112610262</v>
-      </c>
-      <c r="B141" t="n">
-        <v>90168</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>5420</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Phaeolus schweinitzii</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q141" t="n">
-        <v>760099</v>
-      </c>
-      <c r="R141" t="n">
-        <v>7135384</v>
-      </c>
-      <c r="S141" t="n">
-        <v>10</v>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD141" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE141" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG141" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT141" t="inlineStr"/>
-      <c r="AW141" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX141" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>112610310</v>
-      </c>
-      <c r="B142" t="n">
-        <v>56768</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q142" t="n">
-        <v>760210</v>
-      </c>
-      <c r="R142" t="n">
-        <v>7135372</v>
-      </c>
-      <c r="S142" t="n">
-        <v>10</v>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT142" t="inlineStr"/>
-      <c r="AW142" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX142" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>112610354</v>
-      </c>
-      <c r="B143" t="n">
-        <v>77891</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>185</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q143" t="n">
-        <v>760211</v>
-      </c>
-      <c r="R143" t="n">
-        <v>7135137</v>
-      </c>
-      <c r="S143" t="n">
-        <v>10</v>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD143" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE143" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG143" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT143" t="inlineStr"/>
-      <c r="AW143" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX143" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>112610346</v>
-      </c>
-      <c r="B144" t="n">
-        <v>56768</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q144" t="n">
-        <v>760200</v>
-      </c>
-      <c r="R144" t="n">
-        <v>7135128</v>
-      </c>
-      <c r="S144" t="n">
-        <v>10</v>
-      </c>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD144" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE144" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG144" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT144" t="inlineStr"/>
-      <c r="AW144" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>112606276</v>
-      </c>
-      <c r="B145" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q145" t="n">
-        <v>760086</v>
-      </c>
-      <c r="R145" t="n">
-        <v>7135345</v>
-      </c>
-      <c r="S145" t="n">
-        <v>10</v>
-      </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT145" t="inlineStr"/>
-      <c r="AW145" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX145" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>112610471</v>
-      </c>
-      <c r="B146" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q146" t="n">
-        <v>760240</v>
-      </c>
-      <c r="R146" t="n">
-        <v>7135158</v>
-      </c>
-      <c r="S146" t="n">
-        <v>10</v>
-      </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD146" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE146" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG146" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT146" t="inlineStr"/>
-      <c r="AW146" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX146" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>112610461</v>
-      </c>
-      <c r="B147" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q147" t="n">
-        <v>760038</v>
-      </c>
-      <c r="R147" t="n">
-        <v>7135317</v>
-      </c>
-      <c r="S147" t="n">
-        <v>10</v>
-      </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD147" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE147" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG147" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT147" t="inlineStr"/>
-      <c r="AW147" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX147" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>112610464</v>
-      </c>
-      <c r="B148" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Gravfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q148" t="n">
-        <v>760042</v>
-      </c>
-      <c r="R148" t="n">
-        <v>7135371</v>
-      </c>
-      <c r="S148" t="n">
-        <v>10</v>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>Robertsfors</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>Bygdeå</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT148" t="inlineStr"/>
-      <c r="AW148" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX148" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
